--- a/Slots/其他/Game List_Online.xlsx
+++ b/Slots/其他/Game List_Online.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="179">
   <si>
     <t>GAME ID</t>
   </si>
@@ -548,6 +548,36 @@
   </si>
   <si>
     <t>Mega Way</t>
+  </si>
+  <si>
+    <t>106009</t>
+  </si>
+  <si>
+    <t>SexBomb_AIFHA</t>
+  </si>
+  <si>
+    <t>102009</t>
+  </si>
+  <si>
+    <t>Sugar Rockets</t>
+  </si>
+  <si>
+    <t>101016</t>
+  </si>
+  <si>
+    <t>101016-3.0.0</t>
+  </si>
+  <si>
+    <t>Thunder Boost</t>
+  </si>
+  <si>
+    <t>102007</t>
+  </si>
+  <si>
+    <t>102007-3.0.0</t>
+  </si>
+  <si>
+    <t>Spring Celebration</t>
   </si>
 </sst>
 </file>
@@ -2581,10 +2611,10 @@
         <v>0.02</v>
       </c>
       <c r="S24" s="29">
-        <v>0.93</v>
+        <v>0.9304</v>
       </c>
       <c r="T24" s="29">
-        <v>0.95</v>
+        <v>0.9504</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -2640,10 +2670,10 @@
         <v>31</v>
       </c>
       <c r="S25" s="29">
-        <v>0.95</v>
+        <v>0.9501</v>
       </c>
       <c r="T25" s="29">
-        <v>0.95</v>
+        <v>0.9501</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -3798,7 +3828,7 @@
       <c r="Q44" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="R44" s="22">
+      <c r="R44" s="29">
         <v>0.02</v>
       </c>
       <c r="S44" s="29">
@@ -3810,7 +3840,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="30"/>
-      <c r="B45" s="30"/>
+      <c r="B45" s="31"/>
       <c r="C45" s="22" t="s">
         <v>124</v>
       </c>
@@ -3986,7 +4016,7 @@
         <v>0.9596</v>
       </c>
       <c r="T47" s="47">
-        <v>0.9796</v>
+        <v>0.9596</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
@@ -4168,10 +4198,10 @@
         <v>0.02</v>
       </c>
       <c r="S50" s="47">
-        <v>0.9401</v>
+        <v>0.94</v>
       </c>
       <c r="T50" s="47">
-        <v>0.9601</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
@@ -4227,10 +4257,10 @@
         <v>31</v>
       </c>
       <c r="S51" s="47">
-        <v>0.9601</v>
+        <v>0.96</v>
       </c>
       <c r="T51" s="47">
-        <v>0.9601</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
@@ -4412,10 +4442,10 @@
         <v>0.02</v>
       </c>
       <c r="S54" s="55">
-        <v>0.9402</v>
+        <v>0.9398</v>
       </c>
       <c r="T54" s="55">
-        <v>0.9602</v>
+        <v>0.9598</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
@@ -5510,10 +5540,10 @@
         <v>0.02</v>
       </c>
       <c r="S72" s="39">
-        <v>0.94</v>
+        <v>0.9395</v>
       </c>
       <c r="T72" s="39">
-        <v>0.96</v>
+        <v>0.9595</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
@@ -5569,187 +5599,493 @@
         <v>31</v>
       </c>
       <c r="S73" s="39">
+        <v>0.9595</v>
+      </c>
+      <c r="T73" s="39">
+        <v>0.9595</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="50">
+        <v>45.0</v>
+      </c>
+      <c r="B74" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="C74" s="50"/>
+      <c r="D74" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="E74" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="F74" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="H74" s="50">
+        <v>5.0</v>
+      </c>
+      <c r="I74" s="53">
+        <v>1.0</v>
+      </c>
+      <c r="J74" s="54">
+        <v>1500.0</v>
+      </c>
+      <c r="K74" s="54">
+        <v>4.5E7</v>
+      </c>
+      <c r="L74" s="54">
+        <v>30000.0</v>
+      </c>
+      <c r="M74" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="N74" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="O74" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="P74" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q74" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="R74" s="55">
+        <v>0.02</v>
+      </c>
+      <c r="S74" s="55">
+        <v>0.94</v>
+      </c>
+      <c r="T74" s="55">
         <v>0.96</v>
       </c>
-      <c r="T73" s="39">
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="56"/>
+      <c r="B75" s="57"/>
+      <c r="C75" s="50"/>
+      <c r="D75" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="E75" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="H75" s="58">
+        <v>5.0</v>
+      </c>
+      <c r="I75" s="53">
+        <v>1.0</v>
+      </c>
+      <c r="J75" s="54">
+        <v>1500.0</v>
+      </c>
+      <c r="K75" s="54">
+        <v>4.5E7</v>
+      </c>
+      <c r="L75" s="54">
+        <v>30000.0</v>
+      </c>
+      <c r="M75" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="N75" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="O75" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="P75" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q75" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="R75" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="S75" s="55">
         <v>0.96</v>
       </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="60"/>
-      <c r="B74" s="61"/>
-      <c r="C74" s="62"/>
-      <c r="D74" s="62"/>
-      <c r="E74" s="62"/>
-      <c r="F74" s="62"/>
-      <c r="G74" s="62"/>
-      <c r="H74" s="62"/>
-      <c r="I74" s="62"/>
-      <c r="J74" s="62"/>
-      <c r="K74" s="62"/>
-      <c r="L74" s="62"/>
-      <c r="M74" s="62"/>
-      <c r="N74" s="60"/>
-      <c r="O74" s="60"/>
-      <c r="P74" s="60"/>
-      <c r="Q74" s="60"/>
-      <c r="R74" s="62"/>
-      <c r="S74" s="62"/>
-      <c r="T74" s="62"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="60"/>
-      <c r="B75" s="61"/>
-      <c r="C75" s="62"/>
-      <c r="D75" s="62"/>
-      <c r="E75" s="62"/>
-      <c r="F75" s="62"/>
-      <c r="G75" s="62"/>
-      <c r="H75" s="62"/>
-      <c r="I75" s="62"/>
-      <c r="J75" s="62"/>
-      <c r="K75" s="62"/>
-      <c r="L75" s="62"/>
-      <c r="M75" s="62"/>
-      <c r="N75" s="60"/>
-      <c r="O75" s="60"/>
-      <c r="P75" s="60"/>
-      <c r="Q75" s="60"/>
-      <c r="R75" s="62"/>
-      <c r="S75" s="62"/>
-      <c r="T75" s="62"/>
+      <c r="T75" s="55">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="60"/>
-      <c r="B76" s="61"/>
-      <c r="C76" s="62"/>
-      <c r="D76" s="62"/>
-      <c r="E76" s="62"/>
-      <c r="F76" s="62"/>
-      <c r="G76" s="62"/>
-      <c r="H76" s="62"/>
-      <c r="I76" s="62"/>
-      <c r="J76" s="62"/>
-      <c r="K76" s="62"/>
-      <c r="L76" s="62"/>
-      <c r="M76" s="62"/>
-      <c r="N76" s="60"/>
-      <c r="O76" s="60"/>
-      <c r="P76" s="60"/>
-      <c r="Q76" s="60"/>
-      <c r="R76" s="62"/>
-      <c r="S76" s="62"/>
-      <c r="T76" s="62"/>
+      <c r="A76" s="33">
+        <v>46.0</v>
+      </c>
+      <c r="B76" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D76" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="E76" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F76" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="H76" s="33">
+        <v>243.0</v>
+      </c>
+      <c r="I76" s="33">
+        <v>1.0</v>
+      </c>
+      <c r="J76" s="33">
+        <v>1500.0</v>
+      </c>
+      <c r="K76" s="38">
+        <f t="shared" ref="K76:K81" si="2">L76*J76</f>
+        <v>3000000</v>
+      </c>
+      <c r="L76" s="38">
+        <v>2000.0</v>
+      </c>
+      <c r="M76" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="N76" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="O76" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="P76" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q76" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="R76" s="39">
+        <v>0.02</v>
+      </c>
+      <c r="S76" s="39">
+        <v>0.94</v>
+      </c>
+      <c r="T76" s="39">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="60"/>
-      <c r="B77" s="61"/>
-      <c r="C77" s="62"/>
-      <c r="D77" s="62"/>
-      <c r="E77" s="62"/>
-      <c r="F77" s="62"/>
-      <c r="G77" s="62"/>
-      <c r="H77" s="62"/>
-      <c r="I77" s="62"/>
-      <c r="J77" s="62"/>
-      <c r="K77" s="62"/>
-      <c r="L77" s="62"/>
-      <c r="M77" s="62"/>
-      <c r="N77" s="60"/>
-      <c r="O77" s="60"/>
-      <c r="P77" s="60"/>
-      <c r="Q77" s="60"/>
-      <c r="R77" s="62"/>
-      <c r="S77" s="62"/>
-      <c r="T77" s="62"/>
+      <c r="A77" s="40"/>
+      <c r="B77" s="41"/>
+      <c r="C77" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D77" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="E77" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F77" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="H77" s="33">
+        <v>243.0</v>
+      </c>
+      <c r="I77" s="33">
+        <v>1.0</v>
+      </c>
+      <c r="J77" s="33">
+        <v>1500.0</v>
+      </c>
+      <c r="K77" s="38">
+        <f t="shared" si="2"/>
+        <v>3000000</v>
+      </c>
+      <c r="L77" s="38">
+        <v>2000.0</v>
+      </c>
+      <c r="M77" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="N77" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="O77" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="P77" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q77" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="R77" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="S77" s="39">
+        <v>0.96</v>
+      </c>
+      <c r="T77" s="39">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="60"/>
-      <c r="B78" s="61"/>
-      <c r="C78" s="62"/>
-      <c r="D78" s="62"/>
-      <c r="E78" s="62"/>
-      <c r="F78" s="62"/>
-      <c r="G78" s="62"/>
-      <c r="H78" s="62"/>
-      <c r="I78" s="62"/>
-      <c r="J78" s="62"/>
-      <c r="K78" s="62"/>
-      <c r="L78" s="62"/>
-      <c r="M78" s="62"/>
-      <c r="N78" s="60"/>
-      <c r="O78" s="60"/>
-      <c r="P78" s="60"/>
-      <c r="Q78" s="60"/>
-      <c r="R78" s="62"/>
-      <c r="S78" s="62"/>
-      <c r="T78" s="62"/>
+      <c r="A78" s="33">
+        <v>47.0</v>
+      </c>
+      <c r="B78" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="C78" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D78" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="E78" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F78" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="H78" s="33">
+        <v>32400.0</v>
+      </c>
+      <c r="I78" s="33">
+        <v>1.0</v>
+      </c>
+      <c r="J78" s="33">
+        <v>1500.0</v>
+      </c>
+      <c r="K78" s="38">
+        <f t="shared" si="2"/>
+        <v>4500000</v>
+      </c>
+      <c r="L78" s="38">
+        <v>3000.0</v>
+      </c>
+      <c r="M78" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="N78" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="O78" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="P78" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q78" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="R78" s="39">
+        <v>0.02</v>
+      </c>
+      <c r="S78" s="39">
+        <v>0.94</v>
+      </c>
+      <c r="T78" s="39">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="60"/>
-      <c r="B79" s="61"/>
-      <c r="C79" s="62"/>
-      <c r="D79" s="62"/>
-      <c r="E79" s="62"/>
-      <c r="F79" s="62"/>
-      <c r="G79" s="62"/>
-      <c r="H79" s="62"/>
-      <c r="I79" s="62"/>
-      <c r="J79" s="62"/>
-      <c r="K79" s="62"/>
-      <c r="L79" s="62"/>
-      <c r="M79" s="62"/>
-      <c r="N79" s="60"/>
-      <c r="O79" s="60"/>
-      <c r="P79" s="60"/>
-      <c r="Q79" s="60"/>
-      <c r="R79" s="62"/>
-      <c r="S79" s="62"/>
-      <c r="T79" s="62"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="41"/>
+      <c r="C79" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D79" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="E79" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F79" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="H79" s="33">
+        <v>32400.0</v>
+      </c>
+      <c r="I79" s="33">
+        <v>1.0</v>
+      </c>
+      <c r="J79" s="33">
+        <v>1500.0</v>
+      </c>
+      <c r="K79" s="38">
+        <f t="shared" si="2"/>
+        <v>4500000</v>
+      </c>
+      <c r="L79" s="38">
+        <v>3000.0</v>
+      </c>
+      <c r="M79" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="N79" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="O79" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="P79" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q79" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="R79" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="S79" s="39">
+        <v>0.96</v>
+      </c>
+      <c r="T79" s="39">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="60"/>
-      <c r="B80" s="61"/>
-      <c r="C80" s="62"/>
-      <c r="D80" s="62"/>
-      <c r="E80" s="62"/>
-      <c r="F80" s="62"/>
-      <c r="G80" s="62"/>
-      <c r="H80" s="62"/>
-      <c r="I80" s="62"/>
-      <c r="J80" s="62"/>
-      <c r="K80" s="62"/>
-      <c r="L80" s="62"/>
-      <c r="M80" s="62"/>
-      <c r="N80" s="60"/>
-      <c r="O80" s="60"/>
-      <c r="P80" s="60"/>
-      <c r="Q80" s="60"/>
-      <c r="R80" s="62"/>
-      <c r="S80" s="62"/>
-      <c r="T80" s="62"/>
+      <c r="A80" s="33">
+        <v>48.0</v>
+      </c>
+      <c r="B80" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="D80" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="E80" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="H80" s="33">
+        <v>243.0</v>
+      </c>
+      <c r="I80" s="33">
+        <v>1.0</v>
+      </c>
+      <c r="J80" s="33">
+        <v>1500.0</v>
+      </c>
+      <c r="K80" s="38">
+        <f t="shared" si="2"/>
+        <v>55182000</v>
+      </c>
+      <c r="L80" s="38">
+        <v>36788.0</v>
+      </c>
+      <c r="M80" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="N80" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="O80" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="P80" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q80" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="R80" s="39">
+        <v>0.02</v>
+      </c>
+      <c r="S80" s="39">
+        <v>0.945</v>
+      </c>
+      <c r="T80" s="39">
+        <v>0.965</v>
+      </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="60"/>
-      <c r="B81" s="61"/>
-      <c r="C81" s="62"/>
-      <c r="D81" s="62"/>
-      <c r="E81" s="62"/>
-      <c r="F81" s="62"/>
-      <c r="G81" s="62"/>
-      <c r="H81" s="62"/>
-      <c r="I81" s="62"/>
-      <c r="J81" s="62"/>
-      <c r="K81" s="62"/>
-      <c r="L81" s="62"/>
-      <c r="M81" s="62"/>
-      <c r="N81" s="60"/>
-      <c r="O81" s="60"/>
-      <c r="P81" s="60"/>
-      <c r="Q81" s="60"/>
-      <c r="R81" s="62"/>
-      <c r="S81" s="62"/>
-      <c r="T81" s="62"/>
+      <c r="A81" s="40"/>
+      <c r="B81" s="41"/>
+      <c r="C81" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="D81" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="E81" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F81" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="H81" s="33">
+        <v>243.0</v>
+      </c>
+      <c r="I81" s="33">
+        <v>1.0</v>
+      </c>
+      <c r="J81" s="33">
+        <v>1500.0</v>
+      </c>
+      <c r="K81" s="38">
+        <f t="shared" si="2"/>
+        <v>55182000</v>
+      </c>
+      <c r="L81" s="38">
+        <v>36788.0</v>
+      </c>
+      <c r="M81" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="N81" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="O81" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="P81" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q81" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="R81" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="S81" s="39">
+        <v>0.965</v>
+      </c>
+      <c r="T81" s="39">
+        <v>0.965</v>
+      </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="60"/>
